--- a/207940 Samsung Biologics.xlsx
+++ b/207940 Samsung Biologics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67668883-E384-4E70-8717-5E820EB54ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862C702A-5D52-4EB8-99F9-84DE77265566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28200" yWindow="1500" windowWidth="26460" windowHeight="17940" xr2:uid="{83BA8047-C2E0-43A7-BD8D-F81878882685}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="19050" windowHeight="16100" xr2:uid="{83BA8047-C2E0-43A7-BD8D-F81878882685}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>Shares</t>
   </si>
@@ -211,6 +211,12 @@
   </si>
   <si>
     <t>Taxes</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -346,7 +352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -371,10 +377,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -748,15 +751,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C44DE2-1236-4C01-ABE9-7228D8302B19}">
   <dimension ref="B2:N16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
-    <col min="9" max="11" width="3.28515625" customWidth="1"/>
-    <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
+    <col min="9" max="11" width="3.26953125" customWidth="1"/>
+    <col min="12" max="13" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
@@ -776,10 +779,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="1">
-        <v>980000</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+        <v>1545000</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
@@ -788,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>71.174000000000007</v>
+        <v>46.290951</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
@@ -804,10 +807,10 @@
       </c>
       <c r="M4" s="1">
         <f>+M2*M3/1000</f>
-        <v>69750.52</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+        <v>71519.519295000006</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
@@ -816,14 +819,13 @@
         <v>3</v>
       </c>
       <c r="M5" s="1">
-        <f>1060.081+957+0.354+3.111+39.143+49.142+18.085</f>
-        <v>2126.9159999999997</v>
+        <v>1620</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
@@ -832,14 +834,13 @@
         <v>4</v>
       </c>
       <c r="M6" s="1">
-        <f>1302.223172+194.801</f>
-        <v>1497.0241719999999</v>
+        <v>919</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
@@ -849,10 +850,10 @@
       </c>
       <c r="M7" s="1">
         <f>+M4-M5+M6</f>
-        <v>69120.628172000012</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+        <v>70818.519295000006</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
@@ -862,8 +863,9 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="10"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -871,26 +873,27 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>20</v>
       </c>
@@ -899,15 +902,15 @@
       </c>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="6"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -925,19 +928,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A19B0878-BA7A-4D39-BCBA-9811675534B7}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="2"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="14" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>24</v>
       </c>
@@ -999,7 +1002,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
@@ -1028,7 +1031,7 @@
       </c>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>38</v>
       </c>
@@ -1057,7 +1060,7 @@
       </c>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -1069,7 +1072,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:22" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
         <v>23</v>
       </c>
@@ -1102,68 +1105,68 @@
         <v>946.90300000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="16" t="s">
+    <row r="7" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
       <c r="S7" s="1">
         <v>526.74900000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="16" t="s">
+    <row r="8" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
       <c r="S8" s="1">
         <f>+S6-S7</f>
         <v>420.154</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="16" t="s">
+    <row r="9" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
       <c r="S9" s="1">
         <v>198.85400000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>35</v>
       </c>
@@ -1194,7 +1197,7 @@
         <v>221.29999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
@@ -1215,7 +1218,7 @@
       </c>
       <c r="N11" s="11"/>
     </row>
-    <row r="12" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1236,7 +1239,7 @@
         <v>18.79999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>56</v>
       </c>
@@ -1257,7 +1260,7 @@
         <v>240.09999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>57</v>
       </c>
@@ -1277,7 +1280,7 @@
         <v>60.715000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
@@ -1308,7 +1311,7 @@
         <v>179.38499999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
@@ -1322,7 +1325,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>39</v>
       </c>
@@ -1347,7 +1350,7 @@
       </c>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
@@ -1372,7 +1375,7 @@
       </c>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
@@ -1397,7 +1400,7 @@
       </c>
       <c r="N19" s="11"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>43</v>
       </c>
